--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488257_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488257_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1555</v>
+        <v>7.5533</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0603</v>
+        <v>8.0396</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9048</v>
+        <v>-0.4862</v>
       </c>
       <c r="G2" t="n">
         <v>7.6272</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6957</v>
+        <v>-0.2978</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2037</v>
+        <v>-0.2244</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.492</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2583</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3554</v>
+        <v>4.4592</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3162</v>
+        <v>1.7667</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0391</v>
+        <v>2.6925</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3807</v>
+        <v>-0.8733</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3975</v>
+        <v>-0.9517</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0168</v>
+        <v>0.0784</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0814</v>
+        <v>0.0541</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1335</v>
+        <v>-0.6616</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0522</v>
+        <v>0.7157</v>
       </c>
       <c r="M3" t="n">
-        <v>0.462</v>
+        <v>-0.9274</v>
       </c>
       <c r="N3" t="n">
-        <v>0.531</v>
+        <v>-0.2901</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.6373</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>-2.0382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2234</v>
+        <v>3.7057</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2897</v>
+        <v>-0.1116</v>
       </c>
       <c r="T3" t="n">
-        <v>2.936</v>
+        <v>-0.0258</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3537</v>
+        <v>-0.0858</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3144</v>
+        <v>3.7766</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3144</v>
+        <v>3.7766</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3889</v>
+        <v>3.6326</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1014</v>
+        <v>1.1018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2875</v>
+        <v>2.5308</v>
       </c>
       <c r="G4" t="n">
-        <v>3.112</v>
+        <v>0.8834</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3836</v>
+        <v>0.954</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2717</v>
+        <v>-0.0706</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7258</v>
+        <v>1.8719</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6843</v>
+        <v>1.1977</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0415</v>
+        <v>0.6742</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6138</v>
+        <v>-0.9885</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6993</v>
+        <v>-0.2437</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3131</v>
+        <v>-0.7448</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1853</v>
+        <v>2.594</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7411</v>
+        <v>3.7057</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7755</v>
+        <v>-0.1598</v>
       </c>
       <c r="T4" t="n">
-        <v>1.302</v>
+        <v>-0.2879</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4735</v>
+        <v>0.1281</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3133</v>
+        <v>0.315</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3133</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8476</v>
+        <v>3.3598</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0812</v>
+        <v>3.22</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7664</v>
+        <v>0.1398</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8733</v>
+        <v>3.112</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9517</v>
+        <v>4.3836</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0784</v>
+        <v>-1.2717</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0541</v>
+        <v>3.7258</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6616</v>
+        <v>3.6843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7157</v>
+        <v>0.0415</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9274</v>
+        <v>-0.6138</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2901</v>
+        <v>0.6993</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6373</v>
+        <v>-1.3131</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0382</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>3.7057</v>
+        <v>0.7411</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7232</v>
+        <v>0.7464</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7113</v>
+        <v>0.4206</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.012</v>
+        <v>0.3258</v>
       </c>
       <c r="V5" t="n">
-        <v>3.7766</v>
+        <v>-0.3133</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7766</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3133</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8973</v>
+        <v>2.9279</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5142</v>
+        <v>-0.4465</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3831</v>
+        <v>3.3744</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8834</v>
+        <v>0.3807</v>
       </c>
       <c r="H6" t="n">
-        <v>0.954</v>
+        <v>0.3975</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0706</v>
+        <v>-0.0168</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8719</v>
+        <v>-0.0814</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1977</v>
+        <v>-0.1335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6742</v>
+        <v>0.0522</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9885</v>
+        <v>0.462</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2437</v>
+        <v>0.531</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7448</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>2.594</v>
+        <v>0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7057</v>
+        <v>2.2234</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8951</v>
+        <v>1.8622</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8754</v>
+        <v>1.1733</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0197</v>
+        <v>0.6889</v>
       </c>
       <c r="V6" t="n">
-        <v>0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2311</v>
+        <v>1.4522</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2744</v>
+        <v>-2.1765</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5055</v>
+        <v>3.6286</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7687</v>
@@ -1078,13 +1078,13 @@
         <v>4.2616</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.3118</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0037</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0945</v>
+        <v>0.2176</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3144</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1229</v>
+        <v>0.7527</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1283</v>
+        <v>-1.5579</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0055</v>
+        <v>2.3106</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3962</v>
+        <v>-3.9083</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2611</v>
+        <v>-0.1927</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6574</v>
+        <v>-3.7156</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0415</v>
+        <v>-3.0889</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.6019</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0415</v>
+        <v>-2.487</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4377</v>
+        <v>-0.8194</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2611</v>
+        <v>0.4092</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6989</v>
+        <v>-1.2285</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7793</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5191</v>
+        <v>0.2904</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0869</v>
+        <v>-0.0603</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4322</v>
+        <v>0.3506</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0789</v>
+        <v>0.1671</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5372</v>
+        <v>0.3449</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4583</v>
+        <v>-0.1778</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.9083</v>
+        <v>-0.3962</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1927</v>
+        <v>0.2611</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7156</v>
+        <v>-0.6574</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.0889</v>
+        <v>0.0415</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6019</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.487</v>
+        <v>0.0415</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8194</v>
+        <v>-0.4377</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4092</v>
+        <v>0.2611</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2285</v>
+        <v>-0.6989</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5412</v>
+        <v>0.5633</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0396</v>
+        <v>0.3034</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4984</v>
+        <v>0.2599</v>
       </c>
       <c r="V10" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CAPELLIN</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8416</v>
+        <v>-0.7831</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7208</v>
+        <v>-1.2715</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1207</v>
+        <v>0.4884</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.765</v>
+        <v>-1.6442</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1306</v>
+        <v>0.6244</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8955</v>
+        <v>-2.2686</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.3881</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.9058</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.5178</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1536</v>
+        <v>-2.0322</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1306</v>
+        <v>-0.2814</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2841</v>
+        <v>-1.7508</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9646</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.4087</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0766</v>
+        <v>0.1592</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1094</v>
+        <v>0.0473</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0328</v>
+        <v>0.1119</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2578</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2578</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>J. RODRIGUEZ CAPELLIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9062</v>
+        <v>-0.7923</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2715</v>
+        <v>-0.7208</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3653</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.6442</v>
+        <v>-0.765</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6244</v>
+        <v>0.1306</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2686</v>
+        <v>-0.8955</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3881</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9058</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5178</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.0322</v>
+        <v>-0.1536</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2814</v>
+        <v>0.1306</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7508</v>
+        <v>-0.2841</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9646</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0361</v>
+        <v>-0.0274</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0473</v>
+        <v>-0.1094</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0112</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2578</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2578</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.252</v>
+        <v>-3.2509</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9139</v>
+        <v>-2.1098</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3381</v>
+        <v>-1.1411</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3428</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3735</v>
+        <v>-0.3724</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1131</v>
+        <v>-0.309</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2604</v>
+        <v>-0.0634</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2033</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.2667</v>
+        <v>-3.8252</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.8457</v>
+        <v>-2.5519</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4211</v>
+        <v>-1.2733</v>
       </c>
       <c r="G14" t="n">
         <v>-3.2217</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4151</v>
+        <v>0.0264</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.383</v>
+        <v>-0.0892</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0321</v>
+        <v>0.1156</v>
       </c>
       <c r="V14" t="n">
         <v>-0.63</v>
@@ -1582,13 +1582,13 @@
         <v>17.2416</v>
       </c>
       <c r="E15" t="n">
-        <v>5.226400000000001</v>
+        <v>5.226399999999998</v>
       </c>
       <c r="F15" t="n">
-        <v>12.015</v>
+        <v>12.0152</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3286000000000007</v>
+        <v>-0.3285999999999998</v>
       </c>
       <c r="H15" t="n">
         <v>6.121899999999999</v>
@@ -1609,7 +1609,7 @@
         <v>-10.0418</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3630000000000002</v>
+        <v>0.363</v>
       </c>
       <c r="O15" t="n">
         <v>-10.4047</v>
@@ -1624,13 +1624,13 @@
         <v>24.0871</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9908</v>
+        <v>2.990700000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9328000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>2.0577</v>
+        <v>2.0579</v>
       </c>
       <c r="V15" t="n">
         <v>3.4622</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1454</v>
+        <v>2.7827</v>
       </c>
       <c r="E16" t="n">
-        <v>2.932</v>
+        <v>3.4216</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7866</v>
+        <v>-0.6389</v>
       </c>
       <c r="G16" t="n">
         <v>4.086</v>
@@ -1702,13 +1702,13 @@
         <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5902</v>
+        <v>-0.9529</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2037</v>
+        <v>-0.7141</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3865</v>
+        <v>-0.2388</v>
       </c>
       <c r="V16" t="n">
         <v>-2.2033</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.482</v>
+        <v>0.679</v>
       </c>
       <c r="E17" t="n">
         <v>-0.7919</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2739</v>
+        <v>1.4709</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2475</v>
@@ -1780,13 +1780,13 @@
         <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7528</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3867</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3661</v>
+        <v>-0.1691</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0242</v>
+        <v>0.0007</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4473</v>
+        <v>0.2514</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4231</v>
+        <v>-0.2507</v>
       </c>
       <c r="G18" t="n">
         <v>3.3157</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3651</v>
+        <v>-0.3886</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1604</v>
+        <v>-0.0354</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5255</v>
+        <v>-0.3532</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2589</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2699</v>
+        <v>-0.6639</v>
       </c>
       <c r="E19" t="n">
         <v>-1.4589</v>
       </c>
       <c r="F19" t="n">
-        <v>1.189</v>
+        <v>0.795</v>
       </c>
       <c r="G19" t="n">
         <v>-3.3779</v>
@@ -1936,13 +1936,13 @@
         <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6464</v>
+        <v>0.2524</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2226</v>
       </c>
       <c r="U19" t="n">
-        <v>0.869</v>
+        <v>0.475</v>
       </c>
       <c r="V19" t="n">
         <v>2.8321</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-1.308</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7473</v>
+        <v>-2.237</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0028</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>2.4729</v>
@@ -2014,13 +2014,13 @@
         <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1908</v>
+        <v>-0.3728</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0473</v>
+        <v>-0.4424</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1435</v>
+        <v>0.0696</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6289</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1781</v>
+        <v>-1.6862</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3258</v>
+        <v>-0.2278</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8523</v>
+        <v>-1.4584</v>
       </c>
       <c r="G21" t="n">
         <v>0.534</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1562</v>
+        <v>-0.6644</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3867</v>
+        <v>-0.2888</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7695</v>
+        <v>-0.3756</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6294</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8</v>
+        <v>-3.3903</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5849</v>
+        <v>-3.6828</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7849</v>
+        <v>0.2925</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0093</v>
@@ -2170,13 +2170,13 @@
         <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2649</v>
+        <v>-0.3255</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0037</v>
+        <v>-0.1016</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2686</v>
+        <v>-0.2239</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3144</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0041</v>
+        <v>-3.7103</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6933</v>
+        <v>-2.3995</v>
       </c>
       <c r="F23" t="n">
         <v>-1.3108</v>
@@ -2248,10 +2248,10 @@
         <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4887</v>
+        <v>-0.1949</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.383</v>
+        <v>-0.0892</v>
       </c>
       <c r="U23" t="n">
         <v>-0.1057</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6592</v>
+        <v>-4.4398</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6164</v>
+        <v>-2.2247</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0427</v>
+        <v>-2.2151</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5507</v>
@@ -2326,13 +2326,13 @@
         <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1995</v>
+        <v>0.0199</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.383</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1835</v>
+        <v>0.0112</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9444</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2372</v>
+        <v>-5.5052</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1758</v>
+        <v>-2.6654</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0614</v>
+        <v>-2.8398</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1766</v>
@@ -2404,13 +2404,13 @@
         <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4599</v>
+        <v>0.1918</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7039</v>
+        <v>0.2142</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.244</v>
+        <v>-0.0224</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6294</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.2414</v>
+        <v>-17.2413</v>
       </c>
       <c r="E26" t="n">
         <v>-12.015</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.2263</v>
+        <v>-5.2264</v>
       </c>
       <c r="G26" t="n">
         <v>0.3285</v>
@@ -2482,13 +2482,13 @@
         <v>12.97</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.9905</v>
+        <v>-2.9909</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.0578</v>
+        <v>-2.0579</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9326999999999999</v>
+        <v>-0.9329</v>
       </c>
       <c r="V26" t="n">
         <v>-3.4622</v>
